--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.97652665753277</v>
+        <v>7.796185581849075</v>
       </c>
       <c r="D2" t="n">
-        <v>47.807666311617</v>
+        <v>7.768745775637762</v>
       </c>
       <c r="E2" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F2" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.18974907126636</v>
+        <v>6.043334224080783</v>
       </c>
       <c r="D3" t="n">
-        <v>37.06123600888292</v>
+        <v>6.022450851443475</v>
       </c>
       <c r="E3" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F3" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.53153669988282</v>
+        <v>7.561374713730959</v>
       </c>
       <c r="D4" t="n">
-        <v>46.3701682339989</v>
+        <v>7.535152338024822</v>
       </c>
       <c r="E4" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F4" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.39875387324339</v>
+        <v>3.47729750440205</v>
       </c>
       <c r="D5" t="n">
-        <v>21.29684780405294</v>
+        <v>3.460737768158603</v>
       </c>
       <c r="E5" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F5" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.93598043239668</v>
+        <v>4.052096820264461</v>
       </c>
       <c r="D6" t="n">
-        <v>24.80021783720364</v>
+        <v>4.030035398545592</v>
       </c>
       <c r="E6" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F6" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.724693396341878</v>
+        <v>0.9302626769055552</v>
       </c>
       <c r="D7" t="n">
-        <v>5.789960627201146</v>
+        <v>0.9408686019201863</v>
       </c>
       <c r="E7" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F7" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>4.880582133495476</v>
+        <v>0.793094596693015</v>
       </c>
       <c r="D8" t="n">
-        <v>4.994370923033228</v>
+        <v>0.8115852749928996</v>
       </c>
       <c r="E8" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F8" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.97004539634616</v>
+        <v>2.432632376906251</v>
       </c>
       <c r="D9" t="n">
-        <v>14.99906161612984</v>
+        <v>2.437347512621099</v>
       </c>
       <c r="E9" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F9" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.31103371633926</v>
+        <v>5.57554297890513</v>
       </c>
       <c r="D10" t="n">
-        <v>34.27816919897371</v>
+        <v>5.570202494833228</v>
       </c>
       <c r="E10" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F10" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.12511097835934</v>
+        <v>5.220330533983394</v>
       </c>
       <c r="D11" t="n">
-        <v>32.26578165835246</v>
+        <v>5.243189519482275</v>
       </c>
       <c r="E11" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F11" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>14.08764258685909</v>
+        <v>2.289241920364602</v>
       </c>
       <c r="D12" t="n">
-        <v>14.19935701341381</v>
+        <v>2.307395514679744</v>
       </c>
       <c r="E12" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F12" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.08336832474141</v>
+        <v>4.07604735277048</v>
       </c>
       <c r="D13" t="n">
-        <v>25.17310200521467</v>
+        <v>4.090629075847384</v>
       </c>
       <c r="E13" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F13" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.8676179462349</v>
+        <v>5.503487916263172</v>
       </c>
       <c r="D14" t="n">
-        <v>33.97864689967367</v>
+        <v>5.521530121196972</v>
       </c>
       <c r="E14" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F14" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.46025494655805</v>
+        <v>6.574791428815684</v>
       </c>
       <c r="D15" t="n">
-        <v>40.52695415749591</v>
+        <v>6.585630050593086</v>
       </c>
       <c r="E15" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F15" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>50.82607999014922</v>
+        <v>8.25923799839925</v>
       </c>
       <c r="D16" t="n">
-        <v>50.93163172099126</v>
+        <v>8.27639015466108</v>
       </c>
       <c r="E16" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F16" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>51.02438554899413</v>
+        <v>8.291462651711546</v>
       </c>
       <c r="D17" t="n">
-        <v>51.19807064585189</v>
+        <v>8.319686479950933</v>
       </c>
       <c r="E17" t="n">
-        <v>14.77482213668855</v>
+        <v>2.400908597211889</v>
       </c>
       <c r="F17" t="n">
-        <v>14.75359713186833</v>
+        <v>2.397459533928603</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
